--- a/TAM2.0_Sequencing_Prework_SMB_v0.4.xlsx
+++ b/TAM2.0_Sequencing_Prework_SMB_v0.4.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Notes — READ ME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="How to read" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="UK&amp;I" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Poland" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Greece" sheetId="4" state="visible" r:id="rId4"/>
@@ -118,7 +118,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -140,11 +140,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -191,6 +235,8 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -556,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A56"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="135" customWidth="1" min="1" max="1"/>
@@ -576,318 +622,169 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Notes:</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
+          <t>How to read this workbook:</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1. Unlike the PPT exercise we did for Genius, this is a geo × segment view.</t>
+          <t>• Each geo tab opens with the inputs: business priorities and corporate priorities, with the dates by which they must be met.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2. It takes business priorities and corporate priorities as inputs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+          <t>• The Milestones row (▼) places major proposition-related milestones over the horizon in which they land.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>3. It captures the current-state and target-state stack.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+          <t>• Each workstream row shows the current-state stack, the target-state stack, and the planned actions across Now (H2 '26 – H1 '27), Next (H2 '27 – H1 '29) and Later (H2 '29+).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>4. It tracks BUILD, MIGRATE and DECOM decisions on a Now / Next / Later timeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>How to read each geo tab:</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
+          <t>• Actions are tagged: [BUILD] target-state build · [MIGRATE] migration or thin-out · [STOP] stop-sell / stop-integration · [EXIT] decommission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>• Square brackets denote channel context where relevant, e.g. [Bank], [ISV], [Payrix].</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>• Content is scoped to TAM 2.0 — platform-rationalisation actions, not the full BAU roadmap. Where an action enables a stated business priority, the cell says so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>• The INPUTS box holds business priorities and corporate constraints, with the dates they must be met. Segment-level priorities (below) sit above the geo-level priorities captured on each tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
+          <t>• Data centre consolidation is tracked under the Global Infrastructure &amp; Security workstream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>• The Milestones row (▼) places proposition and corporate milestones over the horizon in which they land.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>• The table has one row per workstream: current-state stack, target-state stack, then Now / Next / Later actions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>• All timeline activities are TAM-scoped; BAU roadmap items are excluded. Where an activity directly enables a stated business priority, the cell says so: "[BUILD] … — enabling &lt;priority&gt;".</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
+          <t>• Blue text is a working hypothesis for validation. A blank cell is a request for input — not an indication that nothing is planned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Aggregate priorities (segment-wide, 2026–27):</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>• Tags: [BUILD] = target-state build or adherence · [MIGRATE] = front-book switch, back-book migration or thin-out · [STOP] = stop-sell / stop-integration (frees capacity) · [EXIT] = decommission milestone.</t>
+          <t>• Standardization and platform unification (POM + TAM).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>• Channel / persona context is tagged inline in square brackets where relevant, e.g. [Bank], [ISV], [Wholesale].</t>
+          <t>• Onboarding and activation speed — the core growth bottleneck.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>• Data centre consolidation is tracked under the Global Infrastructure &amp; Security workstream.</t>
+          <t>• VAS monetization — lending, payments optimization, settlement.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>• Horizons: Now = H2 '26 – H1 '27 · Next = H2 '27 – H1 '29 · Later = H2 '29+.</t>
+          <t>• Execution discipline — customer commitments and large rollouts.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>• Blue text is a hypothesis to validate. A blank cell means we need your input — not that nothing is planned.</t>
-        </is>
-      </c>
-    </row>
+          <t>• Migration off legacy and reduction of fragmentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Terminology:</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
+          <t>SMB segment priorities:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>• Sales motion = direct, partner-led, or self-serve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
+          <t>• 2026 — Fix the core experience and onboarding. Accelerate Genius growth and address localization for international expansion (partner-led self-enrollment + lead funnel). Scale VAS and monetization (bundles: Lending, Fee Assist, Disputes / Fraud / Payments). Reduce attrition (portal + onboarding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>• Persona = the partner or customer type within a segment (e.g. Referral, Agent, ISO/Wholesale, Payfac, PFaaS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>• Channel = digital, in-person, or omnichannel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>• Proposition = what the merchant buys (e.g. Genius S, WP360, Revenue Boost). Propositions are inputs and milestones, not an axis of this view.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
+          <t>• 2027 — Global platform standardization across partner, merchant and developer. Fully digital SMB lifecycle (self-serve onboarding and servicing; portal-driven SMB). VAS scaling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Genius S priorities:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>• Platform = the stack itself, current vs target.</t>
+          <t>• Rest of 2026 — Fix onboarding and scalability. Improve merchant experience. Launch Wholesale onboarding (h-TSYS).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>• Persona treatment: SMB is not split by persona; Integrated tags personas inline in brackets; Enterprise is to be decided.</t>
-        </is>
-      </c>
-    </row>
+          <t>• 2027 — Automate onboarding for US/CA. Expand Genius S as a core SMB growth engine. Increase multi-product attach rate (VAS + software).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Open questions:</t>
+          <t>Genius Restaurants priorities:</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>1. Which countries do we consider per region? We want to avoid the long tail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>2. Enterprise: do we split by persona / vertical (region × top 1–4 verticals)? Decide before populating.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>3. Reconcile platform retirement timelines with the data centre consolidation plan — preliminary view requested from infrastructure (an application kept for three years cannot sit in a data centre exiting in one).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>4. North America is intentionally omitted from this June pack — it is sequenced for the Jul 20–21 in-person.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>5. Tabs other than UK&amp;I carry pre-fill from the June QPRs and the earlier straw man — validate or clear with each geo lead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Aggregate priorities (segment-wide, 2026–27):</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>• Standardization and platform unification (POM + TAM).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>• Onboarding and activation speed — the core growth bottleneck.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>• VAS monetization — lending, payments optimization, settlement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>• Execution discipline — customer commitments and large rollouts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>• Migration off legacy and reduction of fragmentation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>SMB segment priorities:</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>• 2026 — Fix the core experience and onboarding. Accelerate Genius growth and address localization for international expansion (partner-led self-enrollment + lead funnel). Scale VAS and monetization (bundles: Lending, Fee Assist, Disputes / Fraud / Payments). Reduce attrition (portal + onboarding).</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>• 2027 — Global platform standardization across partner, merchant and developer. Fully digital SMB lifecycle (self-serve onboarding and servicing; portal-driven SMB). VAS scaling.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Genius S priorities:</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>• Rest of 2026 — Fix onboarding and scalability. Improve merchant experience. Launch Wholesale onboarding (h-TSYS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>• 2027 — Automate onboarding for US/CA. Expand Genius S as a core SMB growth engine. Increase multi-product attach rate (VAS + software).</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Genius Restaurants priorities:</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
           <t>• Under review.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>SMB notes:</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>• SMB is not split by persona. Partner-relevant items carry motion tags inline: [Bank] / [ISV].</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>• Geo priorities and milestones are sourced from the June 2026 QPRs (Hagan pack regional updates; Genius S / Genius R packs).</t>
         </is>
       </c>
     </row>
@@ -920,12 +817,18 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -942,11 +845,15 @@
 5. WP360 — GA into the Irish market Q3 '26; omnichannel hospitality powered by WP eCommerce</t>
         </is>
       </c>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Corporate priorities / constraints</t>
+          <t>Corporate priorities</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -957,13 +864,23 @@
 • Fragmented hGP/hWP sales tooling &amp; portals — operational inefficiency and disjointed merchant journey</t>
         </is>
       </c>
-    </row>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -2185,12 +2102,18 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -2206,11 +2129,15 @@
 4. Cash2card with the eService Pay app (€750k incentive)</t>
         </is>
       </c>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Corporate priorities / constraints</t>
+          <t>Corporate priorities</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -2220,13 +2147,23 @@
 • GP eCom delivery delays and reprioritisation flip plans</t>
         </is>
       </c>
-    </row>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -3184,12 +3121,18 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -3205,11 +3148,15 @@
 4. Genius Mobile — smooth transition from the white-label NBG Pay tom; complete Genius prioritisation analysis for the Greek market</t>
         </is>
       </c>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Corporate priorities / constraints</t>
+          <t>Corporate priorities</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -3219,13 +3166,23 @@
 • Postilion dependency (ACI exit 2029 — corporate)</t>
         </is>
       </c>
-    </row>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -4203,12 +4160,18 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -4225,11 +4188,15 @@
 5. TPV&amp;GO launch (June) — terminals as light EPOS; restaurant, stock and loyalty modules by year-end</t>
         </is>
       </c>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Corporate priorities / constraints</t>
+          <t>Corporate priorities</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -4240,13 +4207,23 @@
 • GP eCom processing/development cost alignment; mid-term GP API &amp; eCom scope</t>
         </is>
       </c>
-    </row>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -5173,12 +5150,18 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -5195,11 +5178,15 @@
 5. eCommerce — Transaction Risk Analysis launch in 4 countries to improve back-book conversion</t>
         </is>
       </c>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Corporate priorities / constraints</t>
+          <t>Corporate priorities</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -5209,13 +5196,23 @@
 • Genius product gap versus competition in Central Europe — reset plan created by Erste-JV leadership and underway</t>
         </is>
       </c>
-    </row>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -6174,12 +6171,18 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -6195,11 +6198,15 @@
 4. IPP solution design — accelerate the productised IPP solution (~35% of Asia P&amp;L) and embed it in transformation plans</t>
         </is>
       </c>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Corporate priorities / constraints</t>
+          <t>Corporate priorities</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -6210,13 +6217,23 @@
 • CYBS Secure Acceptance end of life Jul '27</t>
         </is>
       </c>
-    </row>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -7190,12 +7207,18 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -7208,11 +7231,15 @@
           <t>(populate ahead of June workshop)</t>
         </is>
       </c>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Corporate priorities / constraints</t>
+          <t>Corporate priorities</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
@@ -7220,13 +7247,23 @@
           <t>(populate ahead of June workshop)</t>
         </is>
       </c>
-    </row>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
